--- a/excel.xlsx
+++ b/excel.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,11 @@
           <t>Region</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue_Per_Unit_Sold</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -479,6 +484,9 @@
           <t>North</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -500,6 +508,9 @@
           <t>East</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -521,6 +532,9 @@
           <t>West</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>28.71621621621622</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -542,6 +556,9 @@
           <t>South</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -563,6 +580,9 @@
           <t>North</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -584,6 +604,9 @@
           <t>East</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -605,6 +628,9 @@
           <t>West</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -626,6 +652,9 @@
           <t>South</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>30.74324324324324</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -647,6 +676,9 @@
           <t>North</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -668,6 +700,9 @@
           <t>East</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -689,6 +724,9 @@
           <t>West</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -709,6 +747,9 @@
         <is>
           <t>South</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v>20.28571428571428</v>
       </c>
     </row>
   </sheetData>
